--- a/crosswalk/xlsx/grade-07-world-history-geography__primary-source-crosswalk.xlsx
+++ b/crosswalk/xlsx/grade-07-world-history-geography__primary-source-crosswalk.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -7402,7 +7402,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -10652,7 +10652,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -12980,7 +12980,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -13077,7 +13077,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>NO — agent to verify</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
